--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -2979,12 +2979,12 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>Pembelajaran Mendalam &amp; Jaringan Saraf</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>*AI-Based Smart Service Integration*</t>
+          <t>*Deep Learning &amp; Neural Networks*</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Sem 7</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-416`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
     </row>
@@ -3021,32 +3021,32 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Smart City &amp; Pemerintahan Digital</t>
+          <t>Rekayasa Platform Digital</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>*Smart City &amp; Digital Governance*</t>
+          <t>*Digital Platform Engineering*</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Sem 7</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>`STI-521`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Pembelajaran Mendalam &amp; Jaringan Saraf</t>
+          <t>Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>*Deep Learning &amp; Neural Networks*</t>
+          <t>*AI-Based Smart Service Integration*</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Sem 6</t>
+          <t>Sem 7</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>`STI-413`</t>
+          <t>`STI-413`, `STI-416`</t>
         </is>
       </c>
     </row>
@@ -3100,37 +3100,37 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Rekayasa Platform Digital</t>
+          <t>Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>*Digital Platform Engineering*</t>
+          <t>*Smart City &amp; Digital Governance*</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Sem 6</t>
+          <t>Sem 7</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>`STI-416`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>`STI-627`, `MKU-204`</t>
+          <t>`STI-625`, `MKU-204`</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-624`</t>
+          <t>`STI-413`, `STI-726`</t>
         </is>
       </c>
       <c r="I82" s="9" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>`STI-626`, `STI-521`</t>
+          <t>`STI-624`, `STI-521`</t>
         </is>
       </c>
       <c r="I84" s="9" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -7090,17 +7090,17 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>`STI-728`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>Inovasi Teknologi dan Startup Digital</t>
+          <t>Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>*Technology Innovation and Digital Startup*</t>
+          <t>*AI-Based Smart Service Integration*</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`, `MKU-204`</t>
+          <t>`STI-413`, `STI-416`</t>
         </is>
       </c>
     </row>
@@ -7132,27 +7132,27 @@
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>*AI-Based Smart Service Integration*</t>
+          <t>*Smart City &amp; Digital Governance*</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-416`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
     </row>
@@ -7174,27 +7174,27 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Smart City &amp; Pemerintahan Digital</t>
+          <t>Inovasi Teknologi dan Startup Digital</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>*Smart City &amp; Digital Governance*</t>
+          <t>*Technology Innovation and Digital Startup*</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>`STI-521`</t>
+          <t>`STI-625`, `MKU-204`</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-624` Integrasi AI</t>
+          <t>`STI-413`, `STI-726` Integrasi AI</t>
         </is>
       </c>
       <c r="I221" s="9" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
-          <t>`STI-626`, `STI-521` IoT</t>
+          <t>`STI-624`, `STI-521` IoT</t>
         </is>
       </c>
       <c r="I223" s="9" t="inlineStr">
